--- a/output/graficos_regionales_piramide/plot_regional_piramide_2024_nuble.xlsx
+++ b/output/graficos_regionales_piramide/plot_regional_piramide_2024_nuble.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:23</t>
+    <t xml:space="preserve">2026-09-09 20:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_piramide/plot_regional_piramide_2024_nuble.xlsx
+++ b/output/graficos_regionales_piramide/plot_regional_piramide_2024_nuble.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:20</t>
+    <t xml:space="preserve">2026-09-17 03:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_piramide/plot_regional_piramide_2024_nuble.xlsx
+++ b/output/graficos_regionales_piramide/plot_regional_piramide_2024_nuble.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 03:33</t>
+    <t xml:space="preserve">2026-10-05 21:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
